--- a/ejemplos_briefing/04_operaciones_relevos.xlsx
+++ b/ejemplos_briefing/04_operaciones_relevos.xlsx
@@ -12,6 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relevos Sur" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades Terreno" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Terreno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardian Soberano" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traslados UAC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ops Antartica" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ops Extranjero" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Despliegue Mapa" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,13 +507,69 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Macrozona</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Unidades desplegadas actualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MZN (Macrozona Norte)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MZS (Macrozona Sur)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Antártica</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +593,11 @@
           <t>Unidades</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -550,6 +616,36 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>RR N°6 Pisagua</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Del 25 al 30-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>JAF Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GFE Visviri</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Del 28-06 al 03-07-2026</t>
         </is>
       </c>
     </row>
@@ -564,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +684,11 @@
           <t>Unidades</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -606,6 +707,36 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>RI N°8 Tucapel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Del 27-06 al 02-07-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FT Biobío</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RI N°6 Chacabuco</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Del 30-06 al 05-07-2026</t>
         </is>
       </c>
     </row>
@@ -620,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,6 +844,126 @@
       </c>
       <c r="F3" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Apoyo incendio forestal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JDN Biobío</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BRIFE Concepción</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>desde 22-06-2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Evacuación por aluvión</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JAF Antofagasta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>UFEC Calama</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>desde 21-06-2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Calama</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apoyo albergues</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JDN Araucanía</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UFEC Temuco</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>desde 22-06-2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dotación estival</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BAE O'Higgins</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BAE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>permanente</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Antártica</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -759,11 +1010,353 @@
         <v>540</v>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apoyo a catástrofe y control fronterizo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>JAF</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fuerza actual</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Trabajos de tierra planificados</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Trabajos de tierra ejecutados</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAF Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2.400 Mts</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.850 Mts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JAF Tarapacá</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>320</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5.200 Mts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.600 Mts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JAF Antofagasta</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>185</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.100 Mts</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>940 Mts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UAC</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Unidades trasladadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>I DE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>II DE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>III DE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IV DE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V DE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VI DE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COPE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CGE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DIVEDU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BAE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dotación estival</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CPCCGU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BAE O'Higgins</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Efectivos desplegados</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Repliegue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UNFICYP</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chipre</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apoyo a catástrofe y control fronterizo</t>
+          <t>12-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UNTSO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Medio Oriente</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02-2027</t>
         </is>
       </c>
     </row>
